--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>101.4660069332069</v>
+        <v>16.48822612664612</v>
       </c>
       <c r="D2" t="n">
-        <v>101.6919814220773</v>
+        <v>16.52494698108757</v>
       </c>
       <c r="E2" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F2" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>91.36026323938927</v>
+        <v>14.84604277640076</v>
       </c>
       <c r="D3" t="n">
-        <v>91.54818800539823</v>
+        <v>14.87658055087721</v>
       </c>
       <c r="E3" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F3" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.0831201821801</v>
+        <v>7.001007029604266</v>
       </c>
       <c r="D4" t="n">
-        <v>43.1044934699954</v>
+        <v>7.004480188874252</v>
       </c>
       <c r="E4" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F4" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>74.98641069049199</v>
+        <v>12.18529173720495</v>
       </c>
       <c r="D5" t="n">
-        <v>75.25445068685985</v>
+        <v>12.22884823661473</v>
       </c>
       <c r="E5" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F5" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.83179390098903</v>
+        <v>5.822666508910717</v>
       </c>
       <c r="D6" t="n">
-        <v>36.09168692010179</v>
+        <v>5.86489912451654</v>
       </c>
       <c r="E6" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F6" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.85961877983094</v>
+        <v>4.364688051722529</v>
       </c>
       <c r="D7" t="n">
-        <v>26.53750757204761</v>
+        <v>4.312344980457736</v>
       </c>
       <c r="E7" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F7" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.69980910169826</v>
+        <v>7.101218979025968</v>
       </c>
       <c r="D8" t="n">
-        <v>44.026077232107</v>
+        <v>7.154237550217387</v>
       </c>
       <c r="E8" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F8" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.27065826569441</v>
+        <v>6.706481968175343</v>
       </c>
       <c r="D9" t="n">
-        <v>41.39351397989319</v>
+        <v>6.726446021732642</v>
       </c>
       <c r="E9" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F9" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06632542019376</v>
+        <v>3.423277880781487</v>
       </c>
       <c r="D10" t="n">
-        <v>20.76215927459467</v>
+        <v>3.373850882121633</v>
       </c>
       <c r="E10" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F10" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.21242890515543</v>
+        <v>6.047019697087757</v>
       </c>
       <c r="D11" t="n">
-        <v>36.9525623258479</v>
+        <v>6.004791377950284</v>
       </c>
       <c r="E11" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F11" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.59622943227717</v>
+        <v>4.80938728274504</v>
       </c>
       <c r="D12" t="n">
-        <v>29.9023048838295</v>
+        <v>4.859124543622294</v>
       </c>
       <c r="E12" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F12" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.1545623140225</v>
+        <v>5.387616376028657</v>
       </c>
       <c r="D13" t="n">
-        <v>33.40422744910848</v>
+        <v>5.428186960480128</v>
       </c>
       <c r="E13" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F13" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.05768276869421</v>
+        <v>5.859373449912809</v>
       </c>
       <c r="D14" t="n">
-        <v>35.89970980686199</v>
+        <v>5.833702843615074</v>
       </c>
       <c r="E14" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F14" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.72750025254448</v>
+        <v>3.530718791038478</v>
       </c>
       <c r="D15" t="n">
-        <v>21.96985173497187</v>
+        <v>3.570100906932929</v>
       </c>
       <c r="E15" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F15" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>82.9026709634866</v>
+        <v>13.47168403156657</v>
       </c>
       <c r="D16" t="n">
-        <v>82.64024917305171</v>
+        <v>13.4290404906209</v>
       </c>
       <c r="E16" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F16" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>55.46797146180666</v>
+        <v>9.013545362543582</v>
       </c>
       <c r="D17" t="n">
-        <v>55.30629109887882</v>
+        <v>8.987272303567808</v>
       </c>
       <c r="E17" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F17" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51764755434647</v>
+        <v>2.521617727581302</v>
       </c>
       <c r="D18" t="n">
-        <v>22.27668329228571</v>
+        <v>3.619961034996428</v>
       </c>
       <c r="E18" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F18" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>29.20617409424135</v>
+        <v>4.746003290314219</v>
       </c>
       <c r="D19" t="n">
-        <v>29.11339581814655</v>
+        <v>4.730926820448815</v>
       </c>
       <c r="E19" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F19" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>4.085670589389132</v>
+        <v>0.6639214707757339</v>
       </c>
       <c r="D20" t="n">
-        <v>31.36067433593675</v>
+        <v>5.096109579589721</v>
       </c>
       <c r="E20" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F20" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>15.92732678644133</v>
+        <v>2.588190602796716</v>
       </c>
       <c r="D21" t="n">
-        <v>35.33715230662974</v>
+        <v>5.742287249827333</v>
       </c>
       <c r="E21" t="n">
-        <v>25.7961414916059</v>
+        <v>4.19187299238596</v>
       </c>
       <c r="F21" t="n">
-        <v>23.37875784379712</v>
+        <v>3.799048149617032</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
